--- a/fidelity-corpus/xlsx/inventory/source.xlsx
+++ b/fidelity-corpus/xlsx/inventory/source.xlsx
@@ -462,7 +462,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3083,6 +3083,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
+  <pageSetup paperSize="1" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>